--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_o_higgins.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:30</t>
+    <t xml:space="preserve">2026-09-24 01:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -564,13 +564,13 @@
         <v>-0.27</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>-0.42</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0.15</v>
@@ -584,16 +584,16 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>-0.59</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.04</v>
@@ -610,13 +610,13 @@
         <v>-0.22</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>-0.34</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.12</v>
@@ -633,13 +633,13 @@
         <v>0.2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0.34</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>-0.14</v>
@@ -656,13 +656,13 @@
         <v>0.07</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.47</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>-0.4</v>
@@ -679,13 +679,13 @@
         <v>-0.33</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>-0.53</v>
@@ -699,19 +699,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>-0.03</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="9">
@@ -722,16 +722,16 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>-0.14</v>
@@ -748,13 +748,13 @@
         <v>-0.21</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.42</v>
@@ -771,16 +771,16 @@
         <v>-0.21</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="12">
@@ -794,13 +794,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0.38</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.38</v>
@@ -817,13 +817,13 @@
         <v>-0.05</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0.31</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.36</v>
@@ -840,16 +840,16 @@
         <v>-0.12</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="15">
@@ -860,19 +860,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.06</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="16">
@@ -886,16 +886,16 @@
         <v>-0.28</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="17">
@@ -909,16 +909,16 @@
         <v>-0.4</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="18">
@@ -932,13 +932,13 @@
         <v>-0.82</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>-0.75</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.07</v>
@@ -955,13 +955,13 @@
         <v>-0.4</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>-0.46</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.06</v>
@@ -978,13 +978,13 @@
         <v>-0.35</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>-0.42</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.07</v>
@@ -1001,16 +1001,16 @@
         <v>0.69</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.18</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="22">
@@ -1024,16 +1024,16 @@
         <v>0.42</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.29</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="23">
@@ -1047,13 +1047,13 @@
         <v>0.31</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0.5</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_o_higgins.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:20</t>
+    <t xml:space="preserve">2026-10-01 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_deptot_a_2021_o_higgins.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:21</t>
+    <t xml:space="preserve">2026-10-05 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
